--- a/media/Levels/Level_6.xlsx
+++ b/media/Levels/Level_6.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\oyush\OneDrive - 学校法人新潟総合学院 学校法人国際総合学園 学校法人大彦学園\デスクトップ\勉強\DoctorRemote\DoctorRemote_α\media\Levels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2D1443C4-DE57-45B5-8441-4AF190FED5B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7FD4A5C-E0DF-4DB6-BC85-360EFD25E506}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="753" xr2:uid="{D629F439-E2BD-4112-8312-753BDEB6F601}"/>
   </bookViews>
@@ -473,6 +473,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{938F4841-FA60-445C-98FC-D892E3E9FAF9}">
   <dimension ref="A1:ET150"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="76" max="76" width="8.796875" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:150" x14ac:dyDescent="0.45">
       <c r="F1" s="1">
@@ -6659,13 +6662,13 @@
       <c r="CZ67" s="1">
         <v>0</v>
       </c>
-      <c r="DA67" s="1">
-        <v>0</v>
-      </c>
-      <c r="DB67" s="1">
-        <v>3</v>
-      </c>
-      <c r="DC67" s="1">
+      <c r="DA67" s="6">
+        <v>0</v>
+      </c>
+      <c r="DB67" s="6">
+        <v>8</v>
+      </c>
+      <c r="DC67" s="6">
         <v>0</v>
       </c>
       <c r="DD67" s="1">
@@ -6802,6 +6805,9 @@
       <c r="CP68" s="4">
         <v>0</v>
       </c>
+      <c r="CZ68" s="1">
+        <v>0</v>
+      </c>
       <c r="DO68" s="1">
         <v>0</v>
       </c>
@@ -6903,6 +6909,9 @@
       <c r="CP69" s="4">
         <v>0</v>
       </c>
+      <c r="CZ69" s="1">
+        <v>4</v>
+      </c>
       <c r="DO69" s="1">
         <v>4</v>
       </c>
@@ -7004,6 +7013,9 @@
       <c r="CP70" s="4">
         <v>0</v>
       </c>
+      <c r="CZ70" s="1">
+        <v>0</v>
+      </c>
       <c r="DO70" s="1">
         <v>0</v>
       </c>
@@ -7105,6 +7117,9 @@
       <c r="CP71" s="4">
         <v>0</v>
       </c>
+      <c r="CZ71" s="1">
+        <v>0</v>
+      </c>
       <c r="DO71" s="1">
         <v>0</v>
       </c>
@@ -7191,6 +7206,9 @@
       <c r="CG72" s="2">
         <v>0</v>
       </c>
+      <c r="CZ72" s="1">
+        <v>4</v>
+      </c>
       <c r="DO72" s="1">
         <v>4</v>
       </c>
@@ -7277,6 +7295,9 @@
       <c r="CG73" s="2">
         <v>0</v>
       </c>
+      <c r="CZ73" s="1">
+        <v>0</v>
+      </c>
       <c r="DO73" s="1">
         <v>0</v>
       </c>
@@ -7361,6 +7382,9 @@
         <v>0</v>
       </c>
       <c r="CG74" s="2">
+        <v>0</v>
+      </c>
+      <c r="CZ74" s="6">
         <v>0</v>
       </c>
       <c r="DO74" s="1">
@@ -7512,6 +7536,9 @@
       <c r="CG75" s="2">
         <v>0</v>
       </c>
+      <c r="CZ75" s="6">
+        <v>8</v>
+      </c>
       <c r="DO75" s="1">
         <v>4</v>
       </c>
@@ -7667,6 +7694,9 @@
       <c r="CG76" s="2">
         <v>0</v>
       </c>
+      <c r="CZ76" s="6">
+        <v>0</v>
+      </c>
       <c r="DO76" s="1">
         <v>0</v>
       </c>
@@ -7753,6 +7783,9 @@
       <c r="CG77" s="2">
         <v>0</v>
       </c>
+      <c r="CZ77" s="6">
+        <v>0</v>
+      </c>
       <c r="DO77" s="1">
         <v>0</v>
       </c>
@@ -7839,6 +7872,9 @@
       <c r="CG78" s="2">
         <v>0</v>
       </c>
+      <c r="CZ78" s="6">
+        <v>8</v>
+      </c>
       <c r="DO78" s="1">
         <v>4</v>
       </c>
@@ -7925,6 +7961,9 @@
       <c r="CG79" s="2">
         <v>0</v>
       </c>
+      <c r="CZ79" s="6">
+        <v>0</v>
+      </c>
       <c r="DO79" s="1">
         <v>0</v>
       </c>
@@ -8014,6 +8053,9 @@
       <c r="CG80" s="2">
         <v>0</v>
       </c>
+      <c r="CZ80" s="1">
+        <v>0</v>
+      </c>
       <c r="DO80" s="1">
         <v>0</v>
       </c>
@@ -8118,6 +8160,9 @@
       <c r="CG81" s="2">
         <v>0</v>
       </c>
+      <c r="CZ81" s="1">
+        <v>4</v>
+      </c>
       <c r="DO81" s="1">
         <v>4</v>
       </c>
@@ -8265,6 +8310,9 @@
         <v>0</v>
       </c>
       <c r="CG82" s="2">
+        <v>0</v>
+      </c>
+      <c r="CZ82" s="1">
         <v>0</v>
       </c>
       <c r="DO82" s="1">

--- a/media/Levels/Level_6.xlsx
+++ b/media/Levels/Level_6.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\oyush\OneDrive - 学校法人新潟総合学院 学校法人国際総合学園 学校法人大彦学園\デスクトップ\勉強\DoctorRemote\DoctorRemote_α\media\Levels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7FD4A5C-E0DF-4DB6-BC85-360EFD25E506}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{32A7F900-27E3-4DF9-BF03-1EB742457AF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="753" xr2:uid="{D629F439-E2BD-4112-8312-753BDEB6F601}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Level_6" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>

--- a/media/Levels/Level_6.xlsx
+++ b/media/Levels/Level_6.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\oyush\OneDrive - 学校法人新潟総合学院 学校法人国際総合学園 学校法人大彦学園\デスクトップ\勉強\DoctorRemote\DoctorRemote_α\media\Levels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{32A7F900-27E3-4DF9-BF03-1EB742457AF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{C3E2190B-CC83-4303-BB7A-04FFDC3338AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="753" xr2:uid="{D629F439-E2BD-4112-8312-753BDEB6F601}"/>
   </bookViews>
@@ -5952,9 +5952,6 @@
       <c r="M53" s="1">
         <v>0</v>
       </c>
-      <c r="Y53" s="1">
-        <v>0</v>
-      </c>
       <c r="AH53" s="4">
         <v>0</v>
       </c>
@@ -6017,8 +6014,8 @@
       <c r="M54" s="1">
         <v>4</v>
       </c>
-      <c r="X54" s="1">
-        <v>5</v>
+      <c r="Z54" s="1">
+        <v>0</v>
       </c>
       <c r="AH54" s="4">
         <v>0</v>
@@ -6067,8 +6064,8 @@
       <c r="M55" s="1">
         <v>0</v>
       </c>
-      <c r="W55" s="1">
-        <v>0</v>
+      <c r="Y55" s="1">
+        <v>5</v>
       </c>
       <c r="AH55" s="4">
         <v>0</v>
@@ -6117,7 +6114,7 @@
       <c r="M56" s="1">
         <v>0</v>
       </c>
-      <c r="V56" s="1">
+      <c r="X56" s="1">
         <v>0</v>
       </c>
       <c r="AH56" s="4">
@@ -6167,8 +6164,8 @@
       <c r="M57" s="1">
         <v>4</v>
       </c>
-      <c r="U57" s="1">
-        <v>5</v>
+      <c r="W57" s="1">
+        <v>0</v>
       </c>
       <c r="AH57" s="4">
         <v>0</v>
@@ -6203,8 +6200,8 @@
       <c r="M58" s="1">
         <v>0</v>
       </c>
-      <c r="T58" s="1">
-        <v>0</v>
+      <c r="V58" s="1">
+        <v>5</v>
       </c>
       <c r="AU58" s="1">
         <v>0</v>
@@ -6223,7 +6220,7 @@
       <c r="M59" s="1">
         <v>0</v>
       </c>
-      <c r="S59" s="1">
+      <c r="U59" s="1">
         <v>0</v>
       </c>
       <c r="AU59" s="1">
@@ -6243,8 +6240,8 @@
       <c r="M60" s="1">
         <v>4</v>
       </c>
-      <c r="R60" s="1">
-        <v>5</v>
+      <c r="T60" s="1">
+        <v>0</v>
       </c>
       <c r="AU60" s="1">
         <v>4</v>
@@ -6263,8 +6260,8 @@
       <c r="M61" s="1">
         <v>0</v>
       </c>
-      <c r="Q61" s="1">
-        <v>0</v>
+      <c r="S61" s="1">
+        <v>5</v>
       </c>
       <c r="AU61" s="1">
         <v>0</v>
@@ -6283,7 +6280,7 @@
       <c r="M62" s="1">
         <v>0</v>
       </c>
-      <c r="Q62" s="1">
+      <c r="R62" s="1">
         <v>0</v>
       </c>
       <c r="AU62" s="1">
@@ -6304,7 +6301,7 @@
         <v>5</v>
       </c>
       <c r="R63" s="1">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AU63" s="1">
         <v>4</v>
@@ -6342,7 +6339,7 @@
         <v>0</v>
       </c>
       <c r="S64" s="1">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AU64" s="1">
         <v>0</v>
@@ -6365,6 +6362,9 @@
         <v>0</v>
       </c>
       <c r="S65" s="1">
+        <v>0</v>
+      </c>
+      <c r="T65" s="1">
         <v>0</v>
       </c>
       <c r="AU65" s="1">
@@ -8576,6 +8576,9 @@
       <c r="A85" s="1">
         <v>0</v>
       </c>
+      <c r="J85" s="1">
+        <v>0</v>
+      </c>
       <c r="K85" s="1">
         <v>0</v>
       </c>
@@ -8615,7 +8618,7 @@
         <v>0</v>
       </c>
       <c r="K86" s="1">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="S86" s="1">
         <v>0</v>
@@ -8638,7 +8641,7 @@
         <v>0</v>
       </c>
       <c r="L87" s="1">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="R87" s="1">
         <v>5</v>
@@ -8660,7 +8663,7 @@
       <c r="A88" s="1">
         <v>0</v>
       </c>
-      <c r="M88" s="1">
+      <c r="L88" s="1">
         <v>0</v>
       </c>
       <c r="Q88" s="1">
@@ -8683,8 +8686,8 @@
       <c r="A89" s="1">
         <v>0</v>
       </c>
-      <c r="M89" s="1">
-        <v>0</v>
+      <c r="K89" s="1">
+        <v>5</v>
       </c>
       <c r="Q89" s="1">
         <v>0</v>
@@ -8721,8 +8724,8 @@
       <c r="A90" s="1">
         <v>0</v>
       </c>
-      <c r="L90" s="1">
-        <v>5</v>
+      <c r="J90" s="1">
+        <v>0</v>
       </c>
       <c r="X90" s="1">
         <v>6</v>
@@ -8741,7 +8744,7 @@
       <c r="A91" s="1">
         <v>0</v>
       </c>
-      <c r="K91" s="1">
+      <c r="I91" s="1">
         <v>0</v>
       </c>
       <c r="Y91" s="1">
@@ -8761,8 +8764,8 @@
       <c r="A92" s="1">
         <v>0</v>
       </c>
-      <c r="J92" s="1">
-        <v>0</v>
+      <c r="H92" s="1">
+        <v>5</v>
       </c>
       <c r="Z92" s="1">
         <v>0</v>
@@ -8790,8 +8793,8 @@
       <c r="A93" s="1">
         <v>0</v>
       </c>
-      <c r="I93" s="1">
-        <v>5</v>
+      <c r="G93" s="1">
+        <v>0</v>
       </c>
       <c r="AA93" s="1">
         <v>6</v>
@@ -8816,7 +8819,7 @@
       <c r="A94" s="1">
         <v>0</v>
       </c>
-      <c r="H94" s="1">
+      <c r="F94" s="1">
         <v>0</v>
       </c>
       <c r="AB94" s="1">
@@ -8842,8 +8845,8 @@
       <c r="A95" s="1">
         <v>0</v>
       </c>
-      <c r="G95" s="1">
-        <v>0</v>
+      <c r="E95" s="1">
+        <v>5</v>
       </c>
       <c r="AU95" s="1">
         <v>4</v>
@@ -8865,8 +8868,8 @@
       <c r="A96" s="1">
         <v>0</v>
       </c>
-      <c r="F96" s="1">
-        <v>5</v>
+      <c r="D96" s="1">
+        <v>0</v>
       </c>
       <c r="AU96" s="1">
         <v>0</v>
@@ -8883,9 +8886,6 @@
     </row>
     <row r="97" spans="1:150" x14ac:dyDescent="0.45">
       <c r="A97" s="1">
-        <v>0</v>
-      </c>
-      <c r="E97" s="1">
         <v>0</v>
       </c>
       <c r="AU97" s="5">

--- a/media/Levels/Level_6.xlsx
+++ b/media/Levels/Level_6.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\oyush\OneDrive - 学校法人新潟総合学院 学校法人国際総合学園 学校法人大彦学園\デスクトップ\勉強\DoctorRemote\DoctorRemote_α\media\Levels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C3E2190B-CC83-4303-BB7A-04FFDC3338AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{156B2383-0937-4E28-8789-24D09A05B815}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="753" xr2:uid="{D629F439-E2BD-4112-8312-753BDEB6F601}"/>
   </bookViews>
@@ -6666,7 +6666,7 @@
         <v>0</v>
       </c>
       <c r="DB67" s="6">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="DC67" s="6">
         <v>0</v>

--- a/media/Levels/Level_6.xlsx
+++ b/media/Levels/Level_6.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27726"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\oyush\OneDrive - 学校法人新潟総合学院 学校法人国際総合学園 学校法人大彦学園\デスクトップ\勉強\DoctorRemote\DoctorRemote_α\media\Levels\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\oyush\Desktop\勉強\DoctorRemote\DoctorRemote_α\media\Levels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{156B2383-0937-4E28-8789-24D09A05B815}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{DE23E498-5C2C-4485-BA41-182EE0422684}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="753" xr2:uid="{D629F439-E2BD-4112-8312-753BDEB6F601}"/>
   </bookViews>
@@ -972,66 +972,6 @@
       <c r="BX8" s="1">
         <v>0</v>
       </c>
-      <c r="CM8" s="2">
-        <v>0</v>
-      </c>
-      <c r="CN8" s="2">
-        <v>0</v>
-      </c>
-      <c r="CO8" s="2">
-        <v>0</v>
-      </c>
-      <c r="CP8" s="2">
-        <v>0</v>
-      </c>
-      <c r="CQ8" s="2">
-        <v>0</v>
-      </c>
-      <c r="CR8" s="2">
-        <v>0</v>
-      </c>
-      <c r="CS8" s="2">
-        <v>0</v>
-      </c>
-      <c r="CT8" s="2">
-        <v>0</v>
-      </c>
-      <c r="CU8" s="2">
-        <v>0</v>
-      </c>
-      <c r="CV8" s="2">
-        <v>0</v>
-      </c>
-      <c r="CW8" s="2">
-        <v>0</v>
-      </c>
-      <c r="CX8" s="2">
-        <v>0</v>
-      </c>
-      <c r="CY8" s="2">
-        <v>0</v>
-      </c>
-      <c r="CZ8" s="2">
-        <v>0</v>
-      </c>
-      <c r="DA8" s="2">
-        <v>0</v>
-      </c>
-      <c r="DB8" s="2">
-        <v>0</v>
-      </c>
-      <c r="DC8" s="2">
-        <v>0</v>
-      </c>
-      <c r="DD8" s="2">
-        <v>0</v>
-      </c>
-      <c r="DE8" s="2">
-        <v>0</v>
-      </c>
-      <c r="DF8" s="2">
-        <v>0</v>
-      </c>
       <c r="ET8" s="1">
         <v>0</v>
       </c>
@@ -1043,66 +983,6 @@
       <c r="BX9" s="1">
         <v>4</v>
       </c>
-      <c r="CM9" s="2">
-        <v>0</v>
-      </c>
-      <c r="CN9" s="2">
-        <v>0</v>
-      </c>
-      <c r="CO9" s="2">
-        <v>0</v>
-      </c>
-      <c r="CP9" s="2">
-        <v>0</v>
-      </c>
-      <c r="CQ9" s="2">
-        <v>0</v>
-      </c>
-      <c r="CR9" s="2">
-        <v>0</v>
-      </c>
-      <c r="CS9" s="2">
-        <v>0</v>
-      </c>
-      <c r="CT9" s="2">
-        <v>0</v>
-      </c>
-      <c r="CU9" s="2">
-        <v>0</v>
-      </c>
-      <c r="CV9" s="2">
-        <v>0</v>
-      </c>
-      <c r="CW9" s="2">
-        <v>0</v>
-      </c>
-      <c r="CX9" s="2">
-        <v>0</v>
-      </c>
-      <c r="CY9" s="2">
-        <v>0</v>
-      </c>
-      <c r="CZ9" s="2">
-        <v>0</v>
-      </c>
-      <c r="DA9" s="2">
-        <v>0</v>
-      </c>
-      <c r="DB9" s="2">
-        <v>0</v>
-      </c>
-      <c r="DC9" s="2">
-        <v>0</v>
-      </c>
-      <c r="DD9" s="2">
-        <v>0</v>
-      </c>
-      <c r="DE9" s="2">
-        <v>0</v>
-      </c>
-      <c r="DF9" s="2">
-        <v>0</v>
-      </c>
       <c r="ET9" s="1">
         <v>0</v>
       </c>
@@ -1114,9 +994,6 @@
       <c r="BX10" s="1">
         <v>0</v>
       </c>
-      <c r="CM10" s="2">
-        <v>0</v>
-      </c>
       <c r="CN10" s="2">
         <v>0</v>
       </c>
@@ -1172,6 +1049,9 @@
         <v>0</v>
       </c>
       <c r="DF10" s="2">
+        <v>0</v>
+      </c>
+      <c r="DG10" s="2">
         <v>0</v>
       </c>
       <c r="DK10" s="4">
@@ -1212,9 +1092,6 @@
       <c r="BJ11" s="4">
         <v>0</v>
       </c>
-      <c r="CM11" s="2">
-        <v>0</v>
-      </c>
       <c r="CN11" s="2">
         <v>0</v>
       </c>
@@ -1270,6 +1147,9 @@
         <v>0</v>
       </c>
       <c r="DF11" s="2">
+        <v>0</v>
+      </c>
+      <c r="DG11" s="2">
         <v>0</v>
       </c>
       <c r="DK11" s="4">
@@ -1310,9 +1190,6 @@
       <c r="BJ12" s="4">
         <v>0</v>
       </c>
-      <c r="CM12" s="2">
-        <v>0</v>
-      </c>
       <c r="CN12" s="2">
         <v>0</v>
       </c>
@@ -1368,6 +1245,9 @@
         <v>0</v>
       </c>
       <c r="DF12" s="2">
+        <v>0</v>
+      </c>
+      <c r="DG12" s="2">
         <v>0</v>
       </c>
       <c r="DK12" s="4">
@@ -1408,9 +1288,6 @@
       <c r="BJ13" s="4">
         <v>0</v>
       </c>
-      <c r="CM13" s="2">
-        <v>0</v>
-      </c>
       <c r="CN13" s="2">
         <v>0</v>
       </c>
@@ -1466,6 +1343,9 @@
         <v>0</v>
       </c>
       <c r="DF13" s="2">
+        <v>0</v>
+      </c>
+      <c r="DG13" s="2">
         <v>0</v>
       </c>
       <c r="DK13" s="4">
@@ -1506,9 +1386,6 @@
       <c r="BJ14" s="4">
         <v>0</v>
       </c>
-      <c r="CM14" s="2">
-        <v>0</v>
-      </c>
       <c r="CN14" s="2">
         <v>0</v>
       </c>
@@ -1564,6 +1441,9 @@
         <v>0</v>
       </c>
       <c r="DF14" s="2">
+        <v>0</v>
+      </c>
+      <c r="DG14" s="2">
         <v>0</v>
       </c>
       <c r="DK14" s="4">
@@ -1604,9 +1484,6 @@
       <c r="BJ15" s="4">
         <v>0</v>
       </c>
-      <c r="CM15" s="2">
-        <v>0</v>
-      </c>
       <c r="CN15" s="2">
         <v>0</v>
       </c>
@@ -1662,6 +1539,9 @@
         <v>0</v>
       </c>
       <c r="DF15" s="2">
+        <v>0</v>
+      </c>
+      <c r="DG15" s="2">
         <v>0</v>
       </c>
       <c r="ET15" s="1">
@@ -1672,9 +1552,6 @@
       <c r="A16" s="1">
         <v>0</v>
       </c>
-      <c r="CM16" s="2">
-        <v>0</v>
-      </c>
       <c r="CN16" s="2">
         <v>0</v>
       </c>
@@ -1730,6 +1607,9 @@
         <v>0</v>
       </c>
       <c r="DF16" s="2">
+        <v>0</v>
+      </c>
+      <c r="DG16" s="2">
         <v>0</v>
       </c>
       <c r="ET16" s="1">
@@ -1755,9 +1635,6 @@
       <c r="AX17" s="4">
         <v>0</v>
       </c>
-      <c r="CM17" s="2">
-        <v>0</v>
-      </c>
       <c r="CN17" s="2">
         <v>0</v>
       </c>
@@ -1786,7 +1663,7 @@
         <v>0</v>
       </c>
       <c r="CW17" s="2">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="CX17" s="2">
         <v>0</v>
@@ -1813,6 +1690,9 @@
         <v>0</v>
       </c>
       <c r="DF17" s="2">
+        <v>0</v>
+      </c>
+      <c r="DG17" s="2">
         <v>0</v>
       </c>
       <c r="ET17" s="1">
@@ -1838,9 +1718,6 @@
       <c r="AX18" s="4">
         <v>0</v>
       </c>
-      <c r="CM18" s="2">
-        <v>0</v>
-      </c>
       <c r="CN18" s="2">
         <v>0</v>
       </c>
@@ -1896,6 +1773,9 @@
         <v>0</v>
       </c>
       <c r="DF18" s="2">
+        <v>0</v>
+      </c>
+      <c r="DG18" s="2">
         <v>0</v>
       </c>
       <c r="ET18" s="1">
@@ -1921,9 +1801,6 @@
       <c r="AX19" s="4">
         <v>0</v>
       </c>
-      <c r="CM19" s="2">
-        <v>0</v>
-      </c>
       <c r="CN19" s="2">
         <v>0</v>
       </c>
@@ -1955,7 +1832,7 @@
         <v>0</v>
       </c>
       <c r="CX19" s="2">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="CY19" s="2">
         <v>0</v>
@@ -2085,9 +1962,6 @@
       <c r="BX20" s="1">
         <v>0</v>
       </c>
-      <c r="CM20" s="2">
-        <v>0</v>
-      </c>
       <c r="CN20" s="2">
         <v>0</v>
       </c>
@@ -2143,6 +2017,9 @@
         <v>0</v>
       </c>
       <c r="DF20" s="2">
+        <v>0</v>
+      </c>
+      <c r="DG20" s="2">
         <v>0</v>
       </c>
       <c r="DH20" s="1">
@@ -2249,9 +2126,6 @@
       <c r="BX21" s="1">
         <v>4</v>
       </c>
-      <c r="CM21" s="2">
-        <v>0</v>
-      </c>
       <c r="CN21" s="2">
         <v>0</v>
       </c>
@@ -2307,6 +2181,9 @@
         <v>0</v>
       </c>
       <c r="DF21" s="2">
+        <v>0</v>
+      </c>
+      <c r="DG21" s="2">
         <v>0</v>
       </c>
       <c r="DI21" s="6">
@@ -2398,9 +2275,6 @@
       <c r="BX22" s="1">
         <v>0</v>
       </c>
-      <c r="CM22" s="2">
-        <v>0</v>
-      </c>
       <c r="CN22" s="2">
         <v>0</v>
       </c>
@@ -2456,6 +2330,9 @@
         <v>0</v>
       </c>
       <c r="DF22" s="2">
+        <v>0</v>
+      </c>
+      <c r="DG22" s="2">
         <v>0</v>
       </c>
       <c r="DJ22" s="6">
@@ -2547,9 +2424,6 @@
       <c r="BX23" s="1">
         <v>0</v>
       </c>
-      <c r="CM23" s="2">
-        <v>0</v>
-      </c>
       <c r="CN23" s="2">
         <v>0</v>
       </c>
@@ -2605,6 +2479,9 @@
         <v>0</v>
       </c>
       <c r="DF23" s="2">
+        <v>0</v>
+      </c>
+      <c r="DG23" s="2">
         <v>0</v>
       </c>
       <c r="DK23" s="6">
@@ -2696,9 +2573,6 @@
       <c r="BX24" s="1">
         <v>4</v>
       </c>
-      <c r="CM24" s="2">
-        <v>0</v>
-      </c>
       <c r="CN24" s="2">
         <v>0</v>
       </c>
@@ -2754,6 +2628,9 @@
         <v>0</v>
       </c>
       <c r="DF24" s="2">
+        <v>0</v>
+      </c>
+      <c r="DG24" s="2">
         <v>0</v>
       </c>
       <c r="DL24" s="6">
@@ -2830,9 +2707,6 @@
       <c r="BX25" s="1">
         <v>0</v>
       </c>
-      <c r="CM25" s="2">
-        <v>0</v>
-      </c>
       <c r="CN25" s="2">
         <v>0</v>
       </c>
@@ -2888,11 +2762,17 @@
         <v>0</v>
       </c>
       <c r="DF25" s="2">
+        <v>0</v>
+      </c>
+      <c r="DG25" s="2">
         <v>0</v>
       </c>
       <c r="DM25" s="6">
         <v>10</v>
       </c>
+      <c r="DP25" s="2">
+        <v>0</v>
+      </c>
       <c r="DQ25" s="2">
         <v>0</v>
       </c>
@@ -2948,9 +2828,6 @@
         <v>0</v>
       </c>
       <c r="EI25" s="2">
-        <v>0</v>
-      </c>
-      <c r="EJ25" s="2">
         <v>0</v>
       </c>
       <c r="ET25" s="1">
@@ -3024,9 +2901,6 @@
       <c r="BX26" s="1">
         <v>0</v>
       </c>
-      <c r="CM26" s="2">
-        <v>0</v>
-      </c>
       <c r="CN26" s="2">
         <v>0</v>
       </c>
@@ -3084,9 +2958,15 @@
       <c r="DF26" s="2">
         <v>0</v>
       </c>
+      <c r="DG26" s="2">
+        <v>0</v>
+      </c>
       <c r="DN26" s="6">
         <v>0</v>
       </c>
+      <c r="DP26" s="2">
+        <v>0</v>
+      </c>
       <c r="DQ26" s="2">
         <v>0</v>
       </c>
@@ -3142,9 +3022,6 @@
         <v>0</v>
       </c>
       <c r="EI26" s="2">
-        <v>0</v>
-      </c>
-      <c r="EJ26" s="2">
         <v>0</v>
       </c>
       <c r="ET26" s="1">
@@ -3218,9 +3095,6 @@
       <c r="BX27" s="1">
         <v>4</v>
       </c>
-      <c r="CM27" s="2">
-        <v>0</v>
-      </c>
       <c r="CN27" s="2">
         <v>0</v>
       </c>
@@ -3278,9 +3152,15 @@
       <c r="DF27" s="2">
         <v>0</v>
       </c>
+      <c r="DG27" s="2">
+        <v>0</v>
+      </c>
       <c r="DO27" s="1">
         <v>0</v>
       </c>
+      <c r="DP27" s="2">
+        <v>0</v>
+      </c>
       <c r="DQ27" s="2">
         <v>0</v>
       </c>
@@ -3336,9 +3216,6 @@
         <v>0</v>
       </c>
       <c r="EI27" s="2">
-        <v>0</v>
-      </c>
-      <c r="EJ27" s="2">
         <v>0</v>
       </c>
       <c r="ET27" s="1">
@@ -3412,7 +3289,64 @@
       <c r="BX28" s="1">
         <v>0</v>
       </c>
-      <c r="CV28" s="6">
+      <c r="CN28" s="2">
+        <v>0</v>
+      </c>
+      <c r="CO28" s="2">
+        <v>0</v>
+      </c>
+      <c r="CP28" s="2">
+        <v>0</v>
+      </c>
+      <c r="CQ28" s="2">
+        <v>0</v>
+      </c>
+      <c r="CR28" s="2">
+        <v>0</v>
+      </c>
+      <c r="CS28" s="2">
+        <v>0</v>
+      </c>
+      <c r="CT28" s="2">
+        <v>0</v>
+      </c>
+      <c r="CU28" s="2">
+        <v>0</v>
+      </c>
+      <c r="CV28" s="5">
+        <v>0</v>
+      </c>
+      <c r="CW28" s="2">
+        <v>0</v>
+      </c>
+      <c r="CX28" s="2">
+        <v>0</v>
+      </c>
+      <c r="CY28" s="2">
+        <v>0</v>
+      </c>
+      <c r="CZ28" s="2">
+        <v>0</v>
+      </c>
+      <c r="DA28" s="2">
+        <v>0</v>
+      </c>
+      <c r="DB28" s="2">
+        <v>0</v>
+      </c>
+      <c r="DC28" s="2">
+        <v>0</v>
+      </c>
+      <c r="DD28" s="2">
+        <v>0</v>
+      </c>
+      <c r="DE28" s="2">
+        <v>0</v>
+      </c>
+      <c r="DF28" s="2">
+        <v>0</v>
+      </c>
+      <c r="DG28" s="2">
         <v>0</v>
       </c>
       <c r="DP28" s="1">
@@ -3475,9 +3409,6 @@
       <c r="EI28" s="2">
         <v>0</v>
       </c>
-      <c r="EJ28" s="2">
-        <v>0</v>
-      </c>
       <c r="ET28" s="1">
         <v>0</v>
       </c>
@@ -3549,9 +3480,69 @@
       <c r="BX29" s="1">
         <v>0</v>
       </c>
-      <c r="CV29" s="6">
+      <c r="CN29" s="2">
+        <v>0</v>
+      </c>
+      <c r="CO29" s="2">
+        <v>0</v>
+      </c>
+      <c r="CP29" s="2">
+        <v>0</v>
+      </c>
+      <c r="CQ29" s="2">
+        <v>0</v>
+      </c>
+      <c r="CR29" s="2">
+        <v>0</v>
+      </c>
+      <c r="CS29" s="2">
+        <v>0</v>
+      </c>
+      <c r="CT29" s="2">
+        <v>0</v>
+      </c>
+      <c r="CU29" s="2">
+        <v>0</v>
+      </c>
+      <c r="CV29" s="5">
         <v>8</v>
       </c>
+      <c r="CW29" s="2">
+        <v>0</v>
+      </c>
+      <c r="CX29" s="2">
+        <v>0</v>
+      </c>
+      <c r="CY29" s="2">
+        <v>0</v>
+      </c>
+      <c r="CZ29" s="2">
+        <v>0</v>
+      </c>
+      <c r="DA29" s="2">
+        <v>0</v>
+      </c>
+      <c r="DB29" s="2">
+        <v>0</v>
+      </c>
+      <c r="DC29" s="2">
+        <v>0</v>
+      </c>
+      <c r="DD29" s="2">
+        <v>0</v>
+      </c>
+      <c r="DE29" s="2">
+        <v>0</v>
+      </c>
+      <c r="DF29" s="2">
+        <v>0</v>
+      </c>
+      <c r="DG29" s="2">
+        <v>0</v>
+      </c>
+      <c r="DP29" s="2">
+        <v>0</v>
+      </c>
       <c r="DQ29" s="2">
         <v>0</v>
       </c>
@@ -3607,9 +3598,6 @@
         <v>0</v>
       </c>
       <c r="EI29" s="2">
-        <v>0</v>
-      </c>
-      <c r="EJ29" s="2">
         <v>0</v>
       </c>
       <c r="ET29" s="1">
@@ -3686,6 +3674,9 @@
       <c r="CV30" s="5">
         <v>0</v>
       </c>
+      <c r="DP30" s="2">
+        <v>0</v>
+      </c>
       <c r="DQ30" s="2">
         <v>0</v>
       </c>
@@ -3741,9 +3732,6 @@
         <v>0</v>
       </c>
       <c r="EI30" s="2">
-        <v>0</v>
-      </c>
-      <c r="EJ30" s="2">
         <v>0</v>
       </c>
       <c r="ET30" s="1">
@@ -3820,6 +3808,9 @@
       <c r="CV31" s="5">
         <v>0</v>
       </c>
+      <c r="DP31" s="2">
+        <v>0</v>
+      </c>
       <c r="DQ31" s="2">
         <v>0</v>
       </c>
@@ -3875,9 +3866,6 @@
         <v>0</v>
       </c>
       <c r="EI31" s="2">
-        <v>0</v>
-      </c>
-      <c r="EJ31" s="2">
         <v>0</v>
       </c>
       <c r="ET31" s="1">
@@ -4002,6 +3990,9 @@
       <c r="CV32" s="5">
         <v>8</v>
       </c>
+      <c r="DP32" s="2">
+        <v>0</v>
+      </c>
       <c r="DQ32" s="2">
         <v>0</v>
       </c>
@@ -4057,9 +4048,6 @@
         <v>0</v>
       </c>
       <c r="EI32" s="2">
-        <v>0</v>
-      </c>
-      <c r="EJ32" s="2">
         <v>0</v>
       </c>
       <c r="ET32" s="1">
@@ -4139,6 +4127,9 @@
       <c r="CV33" s="5">
         <v>0</v>
       </c>
+      <c r="DP33" s="2">
+        <v>0</v>
+      </c>
       <c r="DQ33" s="2">
         <v>0</v>
       </c>
@@ -4194,9 +4185,6 @@
         <v>0</v>
       </c>
       <c r="EI33" s="2">
-        <v>0</v>
-      </c>
-      <c r="EJ33" s="2">
         <v>0</v>
       </c>
       <c r="ET33" s="1">
@@ -4276,6 +4264,9 @@
       <c r="CV34" s="5">
         <v>0</v>
       </c>
+      <c r="DP34" s="2">
+        <v>0</v>
+      </c>
       <c r="DQ34" s="2">
         <v>0</v>
       </c>
@@ -4304,10 +4295,10 @@
         <v>0</v>
       </c>
       <c r="DZ34" s="2">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="EA34" s="2">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="EB34" s="2">
         <v>0</v>
@@ -4331,9 +4322,6 @@
         <v>0</v>
       </c>
       <c r="EI34" s="2">
-        <v>0</v>
-      </c>
-      <c r="EJ34" s="2">
         <v>0</v>
       </c>
       <c r="ET34" s="1">
@@ -4413,6 +4401,9 @@
       <c r="CV35" s="5">
         <v>8</v>
       </c>
+      <c r="DP35" s="2">
+        <v>0</v>
+      </c>
       <c r="DQ35" s="2">
         <v>0</v>
       </c>
@@ -4468,9 +4459,6 @@
         <v>0</v>
       </c>
       <c r="EI35" s="2">
-        <v>0</v>
-      </c>
-      <c r="EJ35" s="2">
         <v>0</v>
       </c>
       <c r="ET35" s="1">
@@ -4550,6 +4538,9 @@
       <c r="CV36" s="5">
         <v>0</v>
       </c>
+      <c r="DP36" s="2">
+        <v>0</v>
+      </c>
       <c r="DQ36" s="2">
         <v>0</v>
       </c>
@@ -4605,9 +4596,6 @@
         <v>0</v>
       </c>
       <c r="EI36" s="2">
-        <v>0</v>
-      </c>
-      <c r="EJ36" s="2">
         <v>0</v>
       </c>
       <c r="ET36" s="1">
@@ -4687,6 +4675,9 @@
       <c r="CW37" s="1">
         <v>0</v>
       </c>
+      <c r="DP37" s="2">
+        <v>0</v>
+      </c>
       <c r="DQ37" s="2">
         <v>0</v>
       </c>
@@ -4742,9 +4733,6 @@
         <v>0</v>
       </c>
       <c r="EI37" s="2">
-        <v>0</v>
-      </c>
-      <c r="EJ37" s="2">
         <v>0</v>
       </c>
       <c r="ET37" s="1">
@@ -4824,6 +4812,9 @@
       <c r="CX38" s="1">
         <v>6</v>
       </c>
+      <c r="DP38" s="2">
+        <v>0</v>
+      </c>
       <c r="DQ38" s="2">
         <v>0</v>
       </c>
@@ -4879,9 +4870,6 @@
         <v>0</v>
       </c>
       <c r="EI38" s="2">
-        <v>0</v>
-      </c>
-      <c r="EJ38" s="2">
         <v>0</v>
       </c>
       <c r="ET38" s="1">
@@ -4961,6 +4949,9 @@
       <c r="CY39" s="1">
         <v>0</v>
       </c>
+      <c r="DP39" s="2">
+        <v>0</v>
+      </c>
       <c r="DQ39" s="2">
         <v>0</v>
       </c>
@@ -5016,9 +5007,6 @@
         <v>0</v>
       </c>
       <c r="EI39" s="2">
-        <v>0</v>
-      </c>
-      <c r="EJ39" s="2">
         <v>0</v>
       </c>
       <c r="ET39" s="1">
@@ -5038,6 +5026,9 @@
       <c r="CZ40" s="1">
         <v>0</v>
       </c>
+      <c r="DP40" s="2">
+        <v>0</v>
+      </c>
       <c r="DQ40" s="2">
         <v>0</v>
       </c>
@@ -5093,9 +5084,6 @@
         <v>0</v>
       </c>
       <c r="EI40" s="2">
-        <v>0</v>
-      </c>
-      <c r="EJ40" s="2">
         <v>0</v>
       </c>
       <c r="ET40" s="1">
@@ -5175,9 +5163,6 @@
       <c r="EI41" s="2">
         <v>0</v>
       </c>
-      <c r="EJ41" s="2">
-        <v>0</v>
-      </c>
       <c r="ET41" s="1">
         <v>0</v>
       </c>
@@ -5213,6 +5198,9 @@
       <c r="DO42" s="5">
         <v>0</v>
       </c>
+      <c r="DP42" s="2">
+        <v>0</v>
+      </c>
       <c r="DQ42" s="2">
         <v>0</v>
       </c>
@@ -5268,9 +5256,6 @@
         <v>0</v>
       </c>
       <c r="EI42" s="2">
-        <v>0</v>
-      </c>
-      <c r="EJ42" s="2">
         <v>0</v>
       </c>
       <c r="ET42" s="1">
@@ -5323,6 +5308,9 @@
       <c r="DN43" s="5">
         <v>0</v>
       </c>
+      <c r="DP43" s="2">
+        <v>0</v>
+      </c>
       <c r="DQ43" s="2">
         <v>0</v>
       </c>
@@ -5378,9 +5366,6 @@
         <v>0</v>
       </c>
       <c r="EI43" s="2">
-        <v>0</v>
-      </c>
-      <c r="EJ43" s="2">
         <v>0</v>
       </c>
       <c r="ET43" s="1">
@@ -5433,6 +5418,9 @@
       <c r="DM44" s="5">
         <v>9</v>
       </c>
+      <c r="DP44" s="2">
+        <v>0</v>
+      </c>
       <c r="DQ44" s="2">
         <v>0</v>
       </c>
@@ -5488,9 +5476,6 @@
         <v>0</v>
       </c>
       <c r="EI44" s="2">
-        <v>0</v>
-      </c>
-      <c r="EJ44" s="2">
         <v>0</v>
       </c>
       <c r="ET44" s="1">
